--- a/reponses.xlsx
+++ b/reponses.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="318">
   <si>
     <t>temps_reponse</t>
   </si>
@@ -46,6 +46,444 @@
     <t>Le poids standard d’un cookie Puffy cru est…</t>
   </si>
   <si>
+    <t>Si l’extraction dépasse 32 s, il faut…</t>
+  </si>
+  <si>
+    <t>Le but de remettre le porte-filtre sur la machine après l’avoir essuyé est…</t>
+  </si>
+  <si>
+    <t>Le café utilisé en shop est…</t>
+  </si>
+  <si>
+    <t>Quand tu règles le moulin, tu dois…</t>
+  </si>
+  <si>
+    <t>Entre deux extractions, le porte-filtre se nettoie…</t>
+  </si>
+  <si>
+    <t>Un shot à 27 secondes avec un bon goût en tasse…</t>
+  </si>
+  <si>
+    <t>Après nettoyage, le porte-filtre doit…</t>
+  </si>
+  <si>
+    <t>Si tu fais mousser le lait trop longtemps au bord sans plonger la buse…</t>
+  </si>
+  <si>
+    <t>L’objectif du “pschhh” sur le lait est de…</t>
+  </si>
+  <si>
+    <t>Pour texturer le lait correctement, le vortex sert à…</t>
+  </si>
+  <si>
+    <t>Une fois les bulles créées, la buse vapeur doit être…</t>
+  </si>
+  <si>
+    <t>Pour un cappuccino vs un latte, on…</t>
+  </si>
+  <si>
+    <t>La buse vapeur après chaque boisson doit être…</t>
+  </si>
+  <si>
+    <t>Le matcha doit être conservé…</t>
+  </si>
+  <si>
+    <t>Faire le nettoyage “produit café” du groupe une fois par semaine…</t>
+  </si>
+  <si>
+    <t>Une préparation de matcha en biberon doit être…</t>
+  </si>
+  <si>
+    <t>Le produit de nettoyage “café” sert à…</t>
+  </si>
+  <si>
+    <t>Le matcha perd sa couleur et son goût si…</t>
+  </si>
+  <si>
+    <t>Le produit de nettoyage “lait” sert à…</t>
+  </si>
+  <si>
+    <t>La balance entre Nicaragua et Brésil dans notre blend…</t>
+  </si>
+  <si>
+    <t>Pour nettoyer la tête de groupe, il faut d’abord…</t>
+  </si>
+  <si>
+    <t>Le cycle avec filtre aveugle + poudre café se fait…</t>
+  </si>
+  <si>
+    <t>Après un cycle avec produit café, il faut…</t>
+  </si>
+  <si>
+    <t>Purger la buse vapeur après chaque boisson…</t>
+  </si>
+  <si>
+    <t>La grille / support boissons de la machine café doit être…</t>
+  </si>
+  <si>
+    <t>L’objectif du nettoyage quotidien de la machine café est…</t>
+  </si>
+  <si>
+    <t>Les pichets lait doivent être…</t>
+  </si>
+  <si>
+    <t>Nettoyer le bac de récupération sous la grille de la machine café…</t>
+  </si>
+  <si>
+    <t>Si la boisson sort avec un goût “sale” ou rance, premier réflexe…</t>
+  </si>
+  <si>
+    <t>Pendant le service, la buse vapeur doit être nettoyée…</t>
+  </si>
+  <si>
+    <t>Le café qui reste dans le porte-filtre après extraction doit être…</t>
+  </si>
+  <si>
+    <t>Pour la constance en tasse, le plus important est…</t>
+  </si>
+  <si>
+    <t>La formation barista Puffy vise à…</t>
+  </si>
+  <si>
+    <t>Le produit lait doit être utilisé…</t>
+  </si>
+  <si>
+    <t>Quand un client demande des infos sur le café, on répond…</t>
+  </si>
+  <si>
+    <t>La qualité du café Puffy repose surtout sur…</t>
+  </si>
+  <si>
+    <t>Une boule qui fait 115 g doit être…</t>
+  </si>
+  <si>
+    <t>Pour la préparation pâte, le beurre doit être…</t>
+  </si>
+  <si>
+    <t>Les plaques de cuisson doivent être utilisées…</t>
+  </si>
+  <si>
+    <t>Les cookies sont boulés…</t>
+  </si>
+  <si>
+    <t>Le cooldown minimum avant mise en vente est…</t>
+  </si>
+  <si>
+    <t>Cuire des cookies non assez refroidis au four…</t>
+  </si>
+  <si>
+    <t>Un cookie trop chaud et friable doit être…</t>
+  </si>
+  <si>
+    <t>L’objectif de la vitrine est…</t>
+  </si>
+  <si>
+    <t>Les cookies restants en fin de journée…</t>
+  </si>
+  <si>
+    <t>Sur Deliveroo, en cas de cookie manquant sur une commande, on doit…</t>
+  </si>
+  <si>
+    <t>Un client qui demande un cookie encore en cooldown…</t>
+  </si>
+  <si>
+    <t>Le topping incorrect (ex : 2 noisettes au lieu de 3)…</t>
+  </si>
+  <si>
+    <t>La température des plaques de maintien vitrine est autour de…</t>
+  </si>
+  <si>
+    <t>Les cookies en vitrine sont…</t>
+  </si>
+  <si>
+    <t>Les cookies ne sont pas réchauffés individuellement car…</t>
+  </si>
+  <si>
+    <t>Stocker la pâte à cookie à température ambiante…</t>
+  </si>
+  <si>
+    <t>Les allergènes des cookies se trouvent…</t>
+  </si>
+  <si>
+    <t>Un cookie cassé peut être…</t>
+  </si>
+  <si>
+    <t>En production, charger le four avec…</t>
+  </si>
+  <si>
+    <t>Ne pas respecter FIFO en vitrine…</t>
+  </si>
+  <si>
+    <t>La vitrine doit rester…</t>
+  </si>
+  <si>
+    <t>L’objectif de la vitrine Puffy est…</t>
+  </si>
+  <si>
+    <t>Un cookie cassé ou très déformé pour la vente comptoir doit être…</t>
+  </si>
+  <si>
+    <t>Noter les cuissons futures d’un commun accord en équipe…</t>
+  </si>
+  <si>
+    <t>À quel moment faut-il ajouter le sel dans la recette des cookies ?</t>
+  </si>
+  <si>
+    <t>Combien de noisettes doit-on disposer sur un cookie noisette ?</t>
+  </si>
+  <si>
+    <t>Pourquoi faut-il toujours utiliser des plaques froides ?</t>
+  </si>
+  <si>
+    <t>Aucun produit stocké ne doit être…</t>
+  </si>
+  <si>
+    <t>Stocker un bac sans étiquette DLC…</t>
+  </si>
+  <si>
+    <t>Les étiquettes DLC sont imprimées via…</t>
+  </si>
+  <si>
+    <t>Étiqueter au feutre directement sur le bac au lieu d’utiliser Hygie…</t>
+  </si>
+  <si>
+    <t>L’étiquetage est de la responsabilité…</t>
+  </si>
+  <si>
+    <t>Mélanger produits d’entretien et denrées dans un même placard…</t>
+  </si>
+  <si>
+    <t>Garder les produits d’entretien sur le plan de travail près des aliments…</t>
+  </si>
+  <si>
+    <t>Le FIFO en frigo signifie…</t>
+  </si>
+  <si>
+    <t>Laver un torchon de sol et le réutiliser pour le café…</t>
+  </si>
+  <si>
+    <t>Le nettoyage buse vapeur/pichets se fait…</t>
+  </si>
+  <si>
+    <t>Si tu ne sais plus depuis quand un produit est ouvert…</t>
+  </si>
+  <si>
+    <t>Sous la plaque chaude à cookies, il faut…</t>
+  </si>
+  <si>
+    <t>Les gants jetables remplacent…</t>
+  </si>
+  <si>
+    <t>La tenue appropriée inclut…</t>
+  </si>
+  <si>
+    <t>Le matcha doit être gardé…</t>
+  </si>
+  <si>
+    <t>Faire la plonge avec une eau grasse et jamais renouvelée…</t>
+  </si>
+  <si>
+    <t>Nettoyer la buse vapeur une seule fois par service…</t>
+  </si>
+  <si>
+    <t>Un sol humide non signalé…</t>
+  </si>
+  <si>
+    <t>La fiche de nettoyage des toilettes du shop sert à…</t>
+  </si>
+  <si>
+    <t>Utiliser le même chiffon pour toilettes et plan de travail…</t>
+  </si>
+  <si>
+    <t>Le lave-vaisselle doit être…</t>
+  </si>
+  <si>
+    <t>La fiche de nettoyage non remplie mais ménage fait…</t>
+  </si>
+  <si>
+    <t>En cas de doute sur l’état d’un produit (odeur, aspect)…</t>
+  </si>
+  <si>
+    <t>Laisser des cartons au sol dans les zones de préparation…</t>
+  </si>
+  <si>
+    <t>Toilettes client : le nettoyage doit être…</t>
+  </si>
+  <si>
+    <t>Une zone de travail propre signifie…</t>
+  </si>
+  <si>
+    <t>Remettre au frais un produit resté longtemps à température ambiante…</t>
+  </si>
+  <si>
+    <t>Les boîtes doivent être…</t>
+  </si>
+  <si>
+    <t>Hygiène = obligation…</t>
+  </si>
+  <si>
+    <t>Un produit tombé au sol…</t>
+  </si>
+  <si>
+    <t>Le plan de travail doit être…</t>
+  </si>
+  <si>
+    <t>Les poubelles sans sac plastique…</t>
+  </si>
+  <si>
+    <t>Un torchon de nettoyage pour café (porte-filtre)…</t>
+  </si>
+  <si>
+    <t>Les mains doivent être lavées…</t>
+  </si>
+  <si>
+    <t>Les produits d’entretien doivent être…</t>
+  </si>
+  <si>
+    <t>Laver une coupure à la main et continuer sans pansement…</t>
+  </si>
+  <si>
+    <t>L’hygiène a un impact direct sur…</t>
+  </si>
+  <si>
+    <t>Manger sur le poste de travail…</t>
+  </si>
+  <si>
+    <t>Pourquoi faut-il toujours conserver les produits allergènes séparés et clairement identifiés ?</t>
+  </si>
+  <si>
+    <t>Pourquoi ne faut-il jamais laisser un produit ouvert sans film ou couvercle dans un frigo de service ?</t>
+  </si>
+  <si>
+    <t>Si un frigo affiche 9°C pendant plusieurs heures, que faut-il faire ?</t>
+  </si>
+  <si>
+    <t>Pourquoi faut-il nettoyer chaque jour les étagères, les machines de préparation (batteur, machine café, buse, échelles) et toutes les surfaces autour des postes cookie/café ?</t>
+  </si>
+  <si>
+    <t>Tu arrives au shop : tu commences par…</t>
+  </si>
+  <si>
+    <t>L’arrivée doit se faire…</t>
+  </si>
+  <si>
+    <t>En ouverture, ton premier réflexe opérationnel est…</t>
+  </si>
+  <si>
+    <t>Si le FDC est différent de d'habitude, il faut…</t>
+  </si>
+  <si>
+    <t>Si une référence manque dans la livraison…</t>
+  </si>
+  <si>
+    <t>En fin de journée, il faut imprimer…</t>
+  </si>
+  <si>
+    <t>Sur Inpulse, ne pas déclarer les pertes…</t>
+  </si>
+  <si>
+    <t>La télécollecte TPE doit être…</t>
+  </si>
+  <si>
+    <t>Un client te parle mal pendant un rush…</t>
+  </si>
+  <si>
+    <t>Les chèques-vacances sont…</t>
+  </si>
+  <si>
+    <t>Les tickets restaurant papiers doivent être saisis…</t>
+  </si>
+  <si>
+    <t>Tu fais une erreur sur le mode de paiement en caisse…</t>
+  </si>
+  <si>
+    <t>Billet de 50 € très bizarre au toucher et note de 6 €…</t>
+  </si>
+  <si>
+    <t>Un client demande de réchauffer son cookie dans le four…</t>
+  </si>
+  <si>
+    <t>En fin de journée, CB du Z doit…</t>
+  </si>
+  <si>
+    <t>Tu vois un collègue débordé en plein rush café…</t>
+  </si>
+  <si>
+    <t>En fin de journée, espèces du tiroir (hors FDC) doivent…</t>
+  </si>
+  <si>
+    <t>En cas de conflit entre deux équipiers en plein service…</t>
+  </si>
+  <si>
+    <t>Si CB Z ≠ télécollecte, on…</t>
+  </si>
+  <si>
+    <t>En fin de journée, la pochette de caisse doit contenir…</t>
+  </si>
+  <si>
+    <t>L’outil Inpulse sert surtout à…</t>
+  </si>
+  <si>
+    <t>Une livraison doit être rangée…</t>
+  </si>
+  <si>
+    <t>Un client hésite longtemps en vitrine avec du monde derrière…</t>
+  </si>
+  <si>
+    <t>Une équipe Puffy doit viser…</t>
+  </si>
+  <si>
+    <t>En cas de cookie manquant sur une commande Deliveroo déjà payée, on…</t>
+  </si>
+  <si>
+    <t>Pendant un rush, si un client hésite longtemps, on peut…</t>
+  </si>
+  <si>
+    <t>Phrase de vente recommandée à la caisse…</t>
+  </si>
+  <si>
+    <t>Un client demande des infos allergènes que tu ne connais pas…</t>
+  </si>
+  <si>
+    <t>En fin de service, Combo doit être…</t>
+  </si>
+  <si>
+    <t>Tu as fini ta tâche pendant un moment calme…</t>
+  </si>
+  <si>
+    <t>En cas d’erreur d’encaissement (CB tapée en espèces), il faut…</t>
+  </si>
+  <si>
+    <t>Clôturer une caisse “fausse” pour gagner du temps…</t>
+  </si>
+  <si>
+    <t>Les cookies restants le soir doivent être…</t>
+  </si>
+  <si>
+    <t>Quand un client a beaucoup attendu…</t>
+  </si>
+  <si>
+    <t>Le rôle de l’équipe face à une erreur ou un raté est…</t>
+  </si>
+  <si>
+    <t>Une remarque client négative…</t>
+  </si>
+  <si>
+    <t>La priorité en service est…</t>
+  </si>
+  <si>
+    <t>Ton attendu avec le client…</t>
+  </si>
+  <si>
+    <t>La meilleure attitude face à un problème récurrent…</t>
+  </si>
+  <si>
+    <t>Un client te dit “c’est trop cher”. Comment répondre correctement ?</t>
+  </si>
+  <si>
+    <t>Si un client se trompe dans sa commande et s’en rend compte après coup…</t>
+  </si>
+  <si>
     <t>Q1_choice</t>
   </si>
   <si>
@@ -58,6 +496,444 @@
     <t>C1_choice</t>
   </si>
   <si>
+    <t>Q4_choice</t>
+  </si>
+  <si>
+    <t>Q5_choice</t>
+  </si>
+  <si>
+    <t>Q6_choice</t>
+  </si>
+  <si>
+    <t>Q7_choice</t>
+  </si>
+  <si>
+    <t>Q8_choice</t>
+  </si>
+  <si>
+    <t>Q9_choice</t>
+  </si>
+  <si>
+    <t>Q10_choice</t>
+  </si>
+  <si>
+    <t>Q11_choice</t>
+  </si>
+  <si>
+    <t>Q12_choice</t>
+  </si>
+  <si>
+    <t>Q13_choice</t>
+  </si>
+  <si>
+    <t>Q14_choice</t>
+  </si>
+  <si>
+    <t>Q15_choice</t>
+  </si>
+  <si>
+    <t>Q16_choice</t>
+  </si>
+  <si>
+    <t>Q17_choice</t>
+  </si>
+  <si>
+    <t>Q18_choice</t>
+  </si>
+  <si>
+    <t>Q19_choice</t>
+  </si>
+  <si>
+    <t>Q20_choice</t>
+  </si>
+  <si>
+    <t>Q21_choice</t>
+  </si>
+  <si>
+    <t>Q22_choice</t>
+  </si>
+  <si>
+    <t>Q23_choice</t>
+  </si>
+  <si>
+    <t>Q24_choice</t>
+  </si>
+  <si>
+    <t>Q25_choice</t>
+  </si>
+  <si>
+    <t>Q26_choice</t>
+  </si>
+  <si>
+    <t>Q27_choice</t>
+  </si>
+  <si>
+    <t>Q28_choice</t>
+  </si>
+  <si>
+    <t>Q29_choice</t>
+  </si>
+  <si>
+    <t>Q30_choice</t>
+  </si>
+  <si>
+    <t>Q31_choice</t>
+  </si>
+  <si>
+    <t>Q32_choice</t>
+  </si>
+  <si>
+    <t>Q33_choice</t>
+  </si>
+  <si>
+    <t>Q34_choice</t>
+  </si>
+  <si>
+    <t>Q35_choice</t>
+  </si>
+  <si>
+    <t>Q36_choice</t>
+  </si>
+  <si>
+    <t>Q37_choice</t>
+  </si>
+  <si>
+    <t>Q38_choice</t>
+  </si>
+  <si>
+    <t>Q39_choice</t>
+  </si>
+  <si>
+    <t>C2_choice</t>
+  </si>
+  <si>
+    <t>C3_choice</t>
+  </si>
+  <si>
+    <t>C4_choice</t>
+  </si>
+  <si>
+    <t>C5_choice</t>
+  </si>
+  <si>
+    <t>C6_choice</t>
+  </si>
+  <si>
+    <t>C7_choice</t>
+  </si>
+  <si>
+    <t>C8_choice</t>
+  </si>
+  <si>
+    <t>C9_choice</t>
+  </si>
+  <si>
+    <t>C10_choice</t>
+  </si>
+  <si>
+    <t>C11_choice</t>
+  </si>
+  <si>
+    <t>C12_choice</t>
+  </si>
+  <si>
+    <t>C13_choice</t>
+  </si>
+  <si>
+    <t>C14_choice</t>
+  </si>
+  <si>
+    <t>C15_choice</t>
+  </si>
+  <si>
+    <t>C16_choice</t>
+  </si>
+  <si>
+    <t>C17_choice</t>
+  </si>
+  <si>
+    <t>C18_choice</t>
+  </si>
+  <si>
+    <t>C19_choice</t>
+  </si>
+  <si>
+    <t>C20_choice</t>
+  </si>
+  <si>
+    <t>C21_choice</t>
+  </si>
+  <si>
+    <t>C22_choice</t>
+  </si>
+  <si>
+    <t>C23_choice</t>
+  </si>
+  <si>
+    <t>C24_choice</t>
+  </si>
+  <si>
+    <t>C25_choice</t>
+  </si>
+  <si>
+    <t>C26_choice</t>
+  </si>
+  <si>
+    <t>C27_choice</t>
+  </si>
+  <si>
+    <t>C28_choice</t>
+  </si>
+  <si>
+    <t>H1_choice</t>
+  </si>
+  <si>
+    <t>H2_choice</t>
+  </si>
+  <si>
+    <t>H3_choice</t>
+  </si>
+  <si>
+    <t>H4_choice</t>
+  </si>
+  <si>
+    <t>H5_choice</t>
+  </si>
+  <si>
+    <t>H6_choice</t>
+  </si>
+  <si>
+    <t>H7_choice</t>
+  </si>
+  <si>
+    <t>H8_choice</t>
+  </si>
+  <si>
+    <t>H9_choice</t>
+  </si>
+  <si>
+    <t>H10_choice</t>
+  </si>
+  <si>
+    <t>H11_choice</t>
+  </si>
+  <si>
+    <t>H12_choice</t>
+  </si>
+  <si>
+    <t>H13_choice</t>
+  </si>
+  <si>
+    <t>H14_choice</t>
+  </si>
+  <si>
+    <t>H15_choice</t>
+  </si>
+  <si>
+    <t>H16_choice</t>
+  </si>
+  <si>
+    <t>H17_choice</t>
+  </si>
+  <si>
+    <t>H18_choice</t>
+  </si>
+  <si>
+    <t>H19_choice</t>
+  </si>
+  <si>
+    <t>H20_choice</t>
+  </si>
+  <si>
+    <t>H21_choice</t>
+  </si>
+  <si>
+    <t>H22_choice</t>
+  </si>
+  <si>
+    <t>H23_choice</t>
+  </si>
+  <si>
+    <t>H24_choice</t>
+  </si>
+  <si>
+    <t>H25_choice</t>
+  </si>
+  <si>
+    <t>H26_choice</t>
+  </si>
+  <si>
+    <t>H27_choice</t>
+  </si>
+  <si>
+    <t>H28_choice</t>
+  </si>
+  <si>
+    <t>H29_choice</t>
+  </si>
+  <si>
+    <t>H30_choice</t>
+  </si>
+  <si>
+    <t>H31_choice</t>
+  </si>
+  <si>
+    <t>H32_choice</t>
+  </si>
+  <si>
+    <t>H33_choice</t>
+  </si>
+  <si>
+    <t>H34_choice</t>
+  </si>
+  <si>
+    <t>H35_choice</t>
+  </si>
+  <si>
+    <t>H36_choice</t>
+  </si>
+  <si>
+    <t>H37_choice</t>
+  </si>
+  <si>
+    <t>H38_choice</t>
+  </si>
+  <si>
+    <t>H39_choice</t>
+  </si>
+  <si>
+    <t>H40_choice</t>
+  </si>
+  <si>
+    <t>H41_choice</t>
+  </si>
+  <si>
+    <t>H42_choice</t>
+  </si>
+  <si>
+    <t>S1_choice</t>
+  </si>
+  <si>
+    <t>S2_choice</t>
+  </si>
+  <si>
+    <t>S3_choice</t>
+  </si>
+  <si>
+    <t>S4_choice</t>
+  </si>
+  <si>
+    <t>S5_choice</t>
+  </si>
+  <si>
+    <t>S6_choice</t>
+  </si>
+  <si>
+    <t>S7_choice</t>
+  </si>
+  <si>
+    <t>S8_choice</t>
+  </si>
+  <si>
+    <t>S9_choice</t>
+  </si>
+  <si>
+    <t>S10_choice</t>
+  </si>
+  <si>
+    <t>S11_choice</t>
+  </si>
+  <si>
+    <t>S12_choice</t>
+  </si>
+  <si>
+    <t>S13_choice</t>
+  </si>
+  <si>
+    <t>S14_choice</t>
+  </si>
+  <si>
+    <t>S15_choice</t>
+  </si>
+  <si>
+    <t>S16_choice</t>
+  </si>
+  <si>
+    <t>S17_choice</t>
+  </si>
+  <si>
+    <t>S18_choice</t>
+  </si>
+  <si>
+    <t>S19_choice</t>
+  </si>
+  <si>
+    <t>S20_choice</t>
+  </si>
+  <si>
+    <t>S21_choice</t>
+  </si>
+  <si>
+    <t>S22_choice</t>
+  </si>
+  <si>
+    <t>S23_choice</t>
+  </si>
+  <si>
+    <t>S24_choice</t>
+  </si>
+  <si>
+    <t>S25_choice</t>
+  </si>
+  <si>
+    <t>S26_choice</t>
+  </si>
+  <si>
+    <t>S27_choice</t>
+  </si>
+  <si>
+    <t>S28_choice</t>
+  </si>
+  <si>
+    <t>S29_choice</t>
+  </si>
+  <si>
+    <t>S30_choice</t>
+  </si>
+  <si>
+    <t>S31_choice</t>
+  </si>
+  <si>
+    <t>S32_choice</t>
+  </si>
+  <si>
+    <t>S33_choice</t>
+  </si>
+  <si>
+    <t>S34_choice</t>
+  </si>
+  <si>
+    <t>S35_choice</t>
+  </si>
+  <si>
+    <t>S36_choice</t>
+  </si>
+  <si>
+    <t>S37_choice</t>
+  </si>
+  <si>
+    <t>S38_choice</t>
+  </si>
+  <si>
+    <t>S39_choice</t>
+  </si>
+  <si>
+    <t>S40_choice</t>
+  </si>
+  <si>
+    <t>S41_choice</t>
+  </si>
+  <si>
     <t>00:31</t>
   </si>
   <si>
@@ -80,6 +956,15 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>00:23</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
@@ -532,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:FA4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="7" width="22" customWidth="1"/>
@@ -540,9 +1425,142 @@
     <col min="9" max="9" width="52.2" customWidth="1"/>
     <col min="10" max="10" width="57.6" customWidth="1"/>
     <col min="11" max="11" width="39.6" customWidth="1"/>
+    <col min="12" max="12" width="34.2" customWidth="1"/>
+    <col min="13" max="13" width="60" customWidth="1"/>
+    <col min="14" max="14" width="25.2" customWidth="1"/>
+    <col min="15" max="15" width="31.5" customWidth="1"/>
+    <col min="16" max="16" width="45.9" customWidth="1"/>
+    <col min="17" max="17" width="43.2" customWidth="1"/>
+    <col min="18" max="18" width="34.2" customWidth="1"/>
+    <col min="19" max="19" width="60" customWidth="1"/>
+    <col min="20" max="20" width="37.800000000000004" customWidth="1"/>
+    <col min="21" max="22" width="47.7" customWidth="1"/>
+    <col min="23" max="23" width="31.5" customWidth="1"/>
+    <col min="24" max="24" width="41.4" customWidth="1"/>
+    <col min="25" max="25" width="26.1" customWidth="1"/>
+    <col min="26" max="26" width="58.5" customWidth="1"/>
+    <col min="27" max="27" width="42.300000000000004" customWidth="1"/>
+    <col min="28" max="28" width="34.2" customWidth="1"/>
+    <col min="29" max="29" width="36.9" customWidth="1"/>
+    <col min="30" max="30" width="34.2" customWidth="1"/>
+    <col min="31" max="31" width="48.6" customWidth="1"/>
+    <col min="32" max="32" width="44.1" customWidth="1"/>
+    <col min="33" max="33" width="45.9" customWidth="1"/>
+    <col min="34" max="34" width="37.800000000000004" customWidth="1"/>
+    <col min="35" max="35" width="38.7" customWidth="1"/>
+    <col min="36" max="36" width="52.2" customWidth="1"/>
+    <col min="37" max="37" width="51.300000000000004" customWidth="1"/>
+    <col min="38" max="38" width="27" customWidth="1"/>
+    <col min="39" max="39" width="59.4" customWidth="1"/>
+    <col min="40" max="40" width="58.5" customWidth="1"/>
+    <col min="41" max="41" width="48.6" customWidth="1"/>
+    <col min="42" max="42" width="59.4" customWidth="1"/>
+    <col min="43" max="43" width="45" customWidth="1"/>
+    <col min="44" max="45" width="30.6" customWidth="1"/>
+    <col min="46" max="46" width="51.300000000000004" customWidth="1"/>
+    <col min="47" max="47" width="39.6" customWidth="1"/>
+    <col min="48" max="48" width="31.5" customWidth="1"/>
+    <col min="49" max="50" width="41.4" customWidth="1"/>
+    <col min="51" max="51" width="22" customWidth="1"/>
+    <col min="52" max="52" width="39.6" customWidth="1"/>
+    <col min="53" max="53" width="41.4" customWidth="1"/>
+    <col min="54" max="54" width="37.800000000000004" customWidth="1"/>
+    <col min="55" max="55" width="26.1" customWidth="1"/>
+    <col min="56" max="56" width="35.1" customWidth="1"/>
+    <col min="57" max="57" width="60" customWidth="1"/>
+    <col min="58" max="58" width="45.9" customWidth="1"/>
+    <col min="59" max="59" width="47.7" customWidth="1"/>
+    <col min="60" max="60" width="54.9" customWidth="1"/>
+    <col min="61" max="61" width="25.2" customWidth="1"/>
+    <col min="62" max="62" width="50.4" customWidth="1"/>
+    <col min="63" max="63" width="43.2" customWidth="1"/>
+    <col min="64" max="64" width="35.1" customWidth="1"/>
+    <col min="65" max="65" width="23.400000000000002" customWidth="1"/>
+    <col min="66" max="66" width="32.4" customWidth="1"/>
+    <col min="67" max="67" width="29.7" customWidth="1"/>
+    <col min="68" max="68" width="22" customWidth="1"/>
+    <col min="69" max="69" width="31.5" customWidth="1"/>
+    <col min="70" max="70" width="58.5" customWidth="1"/>
+    <col min="71" max="71" width="50.4" customWidth="1"/>
+    <col min="72" max="72" width="59.4" customWidth="1"/>
+    <col min="73" max="73" width="55.800000000000004" customWidth="1"/>
+    <col min="74" max="74" width="50.4" customWidth="1"/>
+    <col min="75" max="76" width="30.6" customWidth="1"/>
+    <col min="77" max="77" width="34.2" customWidth="1"/>
+    <col min="78" max="78" width="60" customWidth="1"/>
+    <col min="79" max="79" width="34.2" customWidth="1"/>
+    <col min="80" max="80" width="55.800000000000004" customWidth="1"/>
+    <col min="81" max="81" width="60" customWidth="1"/>
+    <col min="82" max="82" width="23.400000000000002" customWidth="1"/>
+    <col min="83" max="83" width="48.6" customWidth="1"/>
+    <col min="84" max="84" width="36.9" customWidth="1"/>
+    <col min="85" max="85" width="48.6" customWidth="1"/>
+    <col min="86" max="86" width="36.9" customWidth="1"/>
+    <col min="87" max="87" width="27" customWidth="1"/>
+    <col min="88" max="88" width="24.3" customWidth="1"/>
+    <col min="89" max="89" width="23.400000000000002" customWidth="1"/>
+    <col min="90" max="90" width="51.300000000000004" customWidth="1"/>
+    <col min="91" max="91" width="45.9" customWidth="1"/>
+    <col min="92" max="92" width="23.400000000000002" customWidth="1"/>
+    <col min="93" max="93" width="45.9" customWidth="1"/>
+    <col min="94" max="94" width="53.1" customWidth="1"/>
+    <col min="95" max="95" width="25.2" customWidth="1"/>
+    <col min="96" max="96" width="45.9" customWidth="1"/>
+    <col min="97" max="97" width="50.4" customWidth="1"/>
+    <col min="98" max="98" width="51.300000000000004" customWidth="1"/>
+    <col min="99" max="99" width="37.800000000000004" customWidth="1"/>
+    <col min="100" max="100" width="32.4" customWidth="1"/>
+    <col min="101" max="101" width="60" customWidth="1"/>
+    <col min="102" max="104" width="22" customWidth="1"/>
+    <col min="105" max="105" width="26.1" customWidth="1"/>
+    <col min="106" max="106" width="29.7" customWidth="1"/>
+    <col min="107" max="107" width="44.1" customWidth="1"/>
+    <col min="108" max="108" width="27" customWidth="1"/>
+    <col min="109" max="109" width="34.2" customWidth="1"/>
+    <col min="110" max="110" width="50.4" customWidth="1"/>
+    <col min="111" max="111" width="29.7" customWidth="1"/>
+    <col min="112" max="112" width="27.900000000000002" customWidth="1"/>
+    <col min="113" max="116" width="60" customWidth="1"/>
+    <col min="117" max="117" width="34.2" customWidth="1"/>
+    <col min="118" max="118" width="22" customWidth="1"/>
+    <col min="119" max="119" width="45.9" customWidth="1"/>
+    <col min="120" max="120" width="42.300000000000004" customWidth="1"/>
+    <col min="121" max="121" width="37.800000000000004" customWidth="1"/>
+    <col min="122" max="122" width="32.4" customWidth="1"/>
+    <col min="123" max="123" width="36" customWidth="1"/>
+    <col min="124" max="124" width="27" customWidth="1"/>
+    <col min="125" max="125" width="35.1" customWidth="1"/>
+    <col min="126" max="126" width="23.400000000000002" customWidth="1"/>
+    <col min="127" max="127" width="45.9" customWidth="1"/>
+    <col min="128" max="128" width="47.7" customWidth="1"/>
+    <col min="129" max="129" width="48.6" customWidth="1"/>
+    <col min="130" max="130" width="50.4" customWidth="1"/>
+    <col min="131" max="131" width="28.8" customWidth="1"/>
+    <col min="132" max="132" width="42.300000000000004" customWidth="1"/>
+    <col min="133" max="134" width="50.4" customWidth="1"/>
+    <col min="135" max="135" width="24.3" customWidth="1"/>
+    <col min="136" max="136" width="49.5" customWidth="1"/>
+    <col min="137" max="138" width="27.900000000000002" customWidth="1"/>
+    <col min="139" max="139" width="54.9" customWidth="1"/>
+    <col min="140" max="140" width="25.2" customWidth="1"/>
+    <col min="141" max="141" width="60" customWidth="1"/>
+    <col min="142" max="142" width="50.4" customWidth="1"/>
+    <col min="143" max="143" width="36" customWidth="1"/>
+    <col min="144" max="144" width="54.9" customWidth="1"/>
+    <col min="145" max="145" width="31.5" customWidth="1"/>
+    <col min="146" max="146" width="39.6" customWidth="1"/>
+    <col min="147" max="147" width="55.800000000000004" customWidth="1"/>
+    <col min="148" max="148" width="45" customWidth="1"/>
+    <col min="149" max="149" width="37.800000000000004" customWidth="1"/>
+    <col min="150" max="150" width="31.5" customWidth="1"/>
+    <col min="151" max="151" width="47.7" customWidth="1"/>
+    <col min="152" max="152" width="26.1" customWidth="1"/>
+    <col min="153" max="154" width="24.3" customWidth="1"/>
+    <col min="155" max="155" width="45.9" customWidth="1"/>
+    <col min="156" max="157" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:157" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,8 +1594,446 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CR1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CS1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CT1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CU1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CV1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CW1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CX1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CY1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CZ1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DA1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DB1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DC1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DD1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DE1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DF1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DG1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DH1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DI1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DJ1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DK1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DL1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DM1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DN1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DO1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="DP1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="DQ1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="DR1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="DS1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="DT1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="DU1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="DV1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="DW1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="DX1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="DY1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="DZ1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="EA1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="EB1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="EC1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="ED1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="EE1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="EF1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="EG1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="EH1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="EI1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="EJ1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="EK1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="EL1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="EM1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="EN1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="EO1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="EP1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="EQ1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="ER1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="ES1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="ET1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="EU1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="EV1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="EW1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="EX1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="EY1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="EZ1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="FA1" s="1" t="s">
+        <v>156</v>
+      </c>
     </row>
-    <row r="2" hidden="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:157" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -600,55 +2056,966 @@
         <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>157</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="K2" t="s">
-        <v>14</v>
+        <v>160</v>
+      </c>
+      <c r="L2" t="s">
+        <v>161</v>
+      </c>
+      <c r="M2" t="s">
+        <v>162</v>
+      </c>
+      <c r="N2" t="s">
+        <v>163</v>
+      </c>
+      <c r="O2" t="s">
+        <v>164</v>
+      </c>
+      <c r="P2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>166</v>
+      </c>
+      <c r="R2" t="s">
+        <v>167</v>
+      </c>
+      <c r="S2" t="s">
+        <v>168</v>
+      </c>
+      <c r="T2" t="s">
+        <v>169</v>
+      </c>
+      <c r="U2" t="s">
+        <v>170</v>
+      </c>
+      <c r="V2" t="s">
+        <v>171</v>
+      </c>
+      <c r="W2" t="s">
+        <v>172</v>
+      </c>
+      <c r="X2" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>180</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>181</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>182</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>184</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>185</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>186</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>188</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>189</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>190</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>191</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>193</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>194</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>195</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>196</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>197</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>198</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>199</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>200</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>201</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>202</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>203</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>204</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>205</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>206</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>207</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>208</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>209</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>210</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>211</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>212</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>213</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>214</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>215</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>216</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>217</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>218</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>219</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>220</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>221</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>222</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>223</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>224</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>225</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>226</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>227</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>228</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>229</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>230</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>231</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>232</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>234</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>235</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>236</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>237</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>238</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>239</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>240</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>241</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>242</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>243</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>244</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>245</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>246</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>247</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>248</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>249</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>250</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>251</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>252</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>253</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>254</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>255</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>256</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>257</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>258</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>259</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>260</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>261</v>
+      </c>
+      <c r="DI2" t="s">
+        <v>262</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>263</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>264</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>265</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>266</v>
+      </c>
+      <c r="DN2" t="s">
+        <v>267</v>
+      </c>
+      <c r="DO2" t="s">
+        <v>268</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>269</v>
+      </c>
+      <c r="DQ2" t="s">
+        <v>270</v>
+      </c>
+      <c r="DR2" t="s">
+        <v>271</v>
+      </c>
+      <c r="DS2" t="s">
+        <v>272</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>273</v>
+      </c>
+      <c r="DU2" t="s">
+        <v>274</v>
+      </c>
+      <c r="DV2" t="s">
+        <v>275</v>
+      </c>
+      <c r="DW2" t="s">
+        <v>276</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>277</v>
+      </c>
+      <c r="DY2" t="s">
+        <v>278</v>
+      </c>
+      <c r="DZ2" t="s">
+        <v>279</v>
+      </c>
+      <c r="EA2" t="s">
+        <v>280</v>
+      </c>
+      <c r="EB2" t="s">
+        <v>281</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>282</v>
+      </c>
+      <c r="ED2" t="s">
+        <v>283</v>
+      </c>
+      <c r="EE2" t="s">
+        <v>284</v>
+      </c>
+      <c r="EF2" t="s">
+        <v>285</v>
+      </c>
+      <c r="EG2" t="s">
+        <v>286</v>
+      </c>
+      <c r="EH2" t="s">
+        <v>287</v>
+      </c>
+      <c r="EI2" t="s">
+        <v>288</v>
+      </c>
+      <c r="EJ2" t="s">
+        <v>289</v>
+      </c>
+      <c r="EK2" t="s">
+        <v>290</v>
+      </c>
+      <c r="EL2" t="s">
+        <v>291</v>
+      </c>
+      <c r="EM2" t="s">
+        <v>292</v>
+      </c>
+      <c r="EN2" t="s">
+        <v>293</v>
+      </c>
+      <c r="EO2" t="s">
+        <v>294</v>
+      </c>
+      <c r="EP2" t="s">
+        <v>295</v>
+      </c>
+      <c r="EQ2" t="s">
+        <v>296</v>
+      </c>
+      <c r="ER2" t="s">
+        <v>297</v>
+      </c>
+      <c r="ES2" t="s">
+        <v>298</v>
+      </c>
+      <c r="ET2" t="s">
+        <v>299</v>
+      </c>
+      <c r="EU2" t="s">
+        <v>300</v>
+      </c>
+      <c r="EV2" t="s">
+        <v>301</v>
+      </c>
+      <c r="EW2" t="s">
+        <v>302</v>
+      </c>
+      <c r="EX2" t="s">
+        <v>303</v>
+      </c>
+      <c r="EY2" t="s">
+        <v>304</v>
+      </c>
+      <c r="EZ2" t="s">
+        <v>305</v>
+      </c>
+      <c r="FA2" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>307</v>
       </c>
       <c r="B3" s="4">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>308</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>18</v>
+        <v>310</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>20</v>
+        <v>312</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>21</v>
+        <v>313</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>22</v>
+        <v>314</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>22</v>
+        <v>314</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>21</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:157" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AM4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AN4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AO4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AP4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AR4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AS4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AT4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AU4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AV4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AW4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AX4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AY4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="AZ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BA4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BB4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BC4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BD4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BE4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BF4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BG4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BH4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BI4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BJ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BK4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BL4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BM4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BN4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BO4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BP4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BQ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BR4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BS4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BT4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BU4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BV4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BW4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BX4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BY4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BZ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CA4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CB4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CC4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CD4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CE4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CF4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CG4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CH4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CI4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CJ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CK4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CL4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CM4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CN4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CO4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CP4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CQ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CR4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CS4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CT4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CU4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CV4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CW4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CX4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CY4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="CZ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DA4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DB4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DC4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DD4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DE4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DF4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DG4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DH4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DI4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DJ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DK4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DL4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DM4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DN4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DO4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DP4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DQ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DR4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DS4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DT4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DU4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DV4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DW4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DX4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DY4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="DZ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EA4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EB4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EC4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="ED4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EE4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EF4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EG4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EH4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EI4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EJ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EK4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EL4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EM4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EN4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EO4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EP4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EQ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="ER4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="ES4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="ET4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EU4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EV4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EW4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EX4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EY4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="EZ4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="FA4" s="3" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/reponses.xlsx
+++ b/reponses.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="319">
   <si>
     <t>temps_reponse</t>
   </si>
@@ -953,6 +953,21 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>00:44</t>
+  </si>
+  <si>
+    <t>Said</t>
+  </si>
+  <si>
+    <t>aaa</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:FA3"/>
+  <dimension ref="A1:FA4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="7" width="22" customWidth="1"/>
@@ -2977,8 +2992,481 @@
         <v>313</v>
       </c>
     </row>
+    <row r="4" spans="1:157" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AM4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AN4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AO4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AP4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AR4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AT4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AU4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AV4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AW4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AX4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AY4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AZ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BA4" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="BB4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BC4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BD4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BE4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BF4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BG4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BH4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BI4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BJ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BK4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BL4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BM4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BN4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BO4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BP4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BQ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BR4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BS4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BT4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BU4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BV4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BW4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BX4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BY4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="BZ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CA4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CB4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CC4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CD4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CE4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CF4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CG4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CH4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CI4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CJ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CK4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CL4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CM4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CN4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CO4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CP4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CQ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CR4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CS4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CT4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CU4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CV4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CW4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CX4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CY4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="CZ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DA4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DB4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DC4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DD4" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="DE4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DF4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DG4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DH4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DI4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DJ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DK4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DL4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DM4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DN4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DO4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DP4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DQ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DR4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DS4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DT4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DU4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DV4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DW4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DX4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DY4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DZ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EA4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EB4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EC4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="ED4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EE4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EF4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EG4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EH4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EI4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EJ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EK4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EL4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EM4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EN4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EO4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EP4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EQ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="ER4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="ES4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="ET4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EU4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EV4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EW4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="EX4" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="EY4" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="EZ4" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="FA4" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>